--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487483_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487483_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2704</v>
+        <v>1.5637</v>
       </c>
       <c r="E2" t="n">
-        <v>1.5175</v>
+        <v>1.3723</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7528</v>
+        <v>0.1915</v>
       </c>
       <c r="G2" t="n">
         <v>1.4047</v>
@@ -610,13 +610,13 @@
         <v>1.5668</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3772</v>
+        <v>0.6706</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7881</v>
+        <v>0.6428</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5891</v>
+        <v>0.0278</v>
       </c>
       <c r="V2" t="n">
         <v>-1.8825</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2012</v>
+        <v>1.1431</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0935</v>
+        <v>0.1958</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1077</v>
+        <v>0.9473</v>
       </c>
       <c r="G3" t="n">
         <v>-0.1229</v>
@@ -688,13 +688,13 @@
         <v>1.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.184</v>
+        <v>-0.242</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.594</v>
+        <v>-0.4917</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4101</v>
+        <v>0.2497</v>
       </c>
       <c r="V3" t="n">
         <v>0.3329</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3944</v>
+        <v>0.6571</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1214</v>
+        <v>2.2238</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.7271</v>
+        <v>-1.5667</v>
       </c>
       <c r="G4" t="n">
         <v>-0.1185</v>
@@ -766,13 +766,13 @@
         <v>1.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2912</v>
+        <v>-0.0285</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1494</v>
+        <v>-0.0471</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1419</v>
+        <v>0.0185</v>
       </c>
       <c r="V4" t="n">
         <v>0.6083</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0462</v>
+        <v>-0.0977</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3936</v>
+        <v>-0.3771</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4397</v>
+        <v>0.2794</v>
       </c>
       <c r="G5" t="n">
         <v>-3.2037</v>
@@ -844,13 +844,13 @@
         <v>2.3502</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2997</v>
+        <v>-1.4436</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3935</v>
+        <v>-0.377</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9062</v>
+        <v>-1.0666</v>
       </c>
       <c r="V5" t="n">
         <v>3.3745</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6044</v>
+        <v>-1.5613</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0424</v>
+        <v>-0.6739000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6468</v>
+        <v>-0.8874</v>
       </c>
       <c r="G6" t="n">
         <v>0.1415</v>
@@ -922,13 +922,13 @@
         <v>2.1543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5813</v>
+        <v>-0.3757</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5617</v>
+        <v>-0.1547</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0196</v>
+        <v>-0.221</v>
       </c>
       <c r="V6" t="n">
         <v>0.4355</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.7958</v>
+        <v>-2.3517</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.345</v>
+        <v>-0.3286</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.4508</v>
+        <v>-2.0231</v>
       </c>
       <c r="G7" t="n">
         <v>-1.694</v>
@@ -1000,13 +1000,13 @@
         <v>2.9377</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.277</v>
+        <v>-0.8328</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1523</v>
+        <v>0.1688</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.4293</v>
+        <v>-1.0016</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6083</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.8911</v>
+        <v>-4.0258</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5559</v>
+        <v>-1.7441</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3352</v>
+        <v>-2.2817</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5292</v>
@@ -1078,13 +1078,13 @@
         <v>0.7834</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.499</v>
+        <v>-0.6337</v>
       </c>
       <c r="T8" t="n">
-        <v>0.26</v>
+        <v>0.0717</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7589</v>
+        <v>-0.7055</v>
       </c>
       <c r="V8" t="n">
         <v>-1.492</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.602</v>
+        <v>-5.8171</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.0719</v>
+        <v>-5.5008</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5301</v>
+        <v>-0.3162</v>
       </c>
       <c r="G9" t="n">
         <v>-4.5661</v>
@@ -1156,13 +1156,13 @@
         <v>0.9792</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.0359</v>
+        <v>-1.251</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9745</v>
+        <v>-0.4035</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0613</v>
+        <v>-0.8475</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.6921</v>
+        <v>-6.5792</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4968</v>
+        <v>-2.4374</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.1952</v>
+        <v>-4.1418</v>
       </c>
       <c r="G10" t="n">
         <v>-4.0415</v>
@@ -1234,13 +1234,13 @@
         <v>0.1958</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.926</v>
+        <v>-0.8131</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4399</v>
+        <v>-0.3805</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.486</v>
+        <v>-0.4326</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9412</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.6487</v>
+        <v>-7.6591</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.5657</v>
+        <v>-3.7899</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.083</v>
+        <v>-3.8692</v>
       </c>
       <c r="G11" t="n">
         <v>-6.5713</v>
@@ -1312,13 +1312,13 @@
         <v>2.3502</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.0359</v>
+        <v>-1.0463</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.331</v>
+        <v>-0.5552</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7049</v>
+        <v>-0.4911</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2166</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-25.3219</v>
+        <v>-24.728</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.6541</v>
+        <v>-11.0599</v>
       </c>
       <c r="F12" t="n">
-        <v>-13.668</v>
+        <v>-13.6679</v>
       </c>
       <c r="G12" t="n">
         <v>-19.301</v>
@@ -1390,13 +1390,13 @@
         <v>15.6678</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.590199999999999</v>
+        <v>-5.9961</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.1202</v>
+        <v>-1.5264</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.4697</v>
+        <v>-4.4699</v>
       </c>
       <c r="V12" t="n">
         <v>-1.389400000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>13.8143</v>
+        <v>12.9643</v>
       </c>
       <c r="E13" t="n">
-        <v>10.0705</v>
+        <v>8.944800000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>3.7438</v>
+        <v>4.0195</v>
       </c>
       <c r="G13" t="n">
         <v>6.375</v>
@@ -1468,13 +1468,13 @@
         <v>2.7419</v>
       </c>
       <c r="S13" t="n">
-        <v>3.0268</v>
+        <v>2.1768</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3949</v>
+        <v>1.2692</v>
       </c>
       <c r="U13" t="n">
-        <v>0.632</v>
+        <v>0.9077</v>
       </c>
       <c r="V13" t="n">
         <v>3.0415</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.774900000000001</v>
+        <v>10.1052</v>
       </c>
       <c r="E14" t="n">
-        <v>4.906</v>
+        <v>5.8271</v>
       </c>
       <c r="F14" t="n">
-        <v>3.8688</v>
+        <v>4.2782</v>
       </c>
       <c r="G14" t="n">
         <v>5.1941</v>
@@ -1546,13 +1546,13 @@
         <v>2.7419</v>
       </c>
       <c r="S14" t="n">
-        <v>0.09</v>
+        <v>1.4203</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3341</v>
+        <v>0.587</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4241</v>
+        <v>0.8334</v>
       </c>
       <c r="V14" t="n">
         <v>3.0991</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.819</v>
+        <v>4.0919</v>
       </c>
       <c r="E15" t="n">
         <v>0.2844</v>
       </c>
       <c r="F15" t="n">
-        <v>3.5346</v>
+        <v>3.8075</v>
       </c>
       <c r="G15" t="n">
         <v>0.6006</v>
@@ -1624,13 +1624,13 @@
         <v>2.1543</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7899</v>
+        <v>1.0628</v>
       </c>
       <c r="T15" t="n">
         <v>0.4493</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3405</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>0.6659</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3142</v>
+        <v>3.4359</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9784</v>
+        <v>0.7738</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3357</v>
+        <v>2.6621</v>
       </c>
       <c r="G16" t="n">
         <v>1.5354</v>
@@ -1702,13 +1702,13 @@
         <v>1.7626</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3295</v>
+        <v>1.4512</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7046</v>
+        <v>0.4999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.625</v>
+        <v>0.9513</v>
       </c>
       <c r="V16" t="n">
         <v>0.0576</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5136</v>
+        <v>2.4659</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7568</v>
+        <v>-1.3475</v>
       </c>
       <c r="F17" t="n">
-        <v>3.2704</v>
+        <v>3.8134</v>
       </c>
       <c r="G17" t="n">
         <v>3.5909</v>
@@ -1780,13 +1780,13 @@
         <v>2.7419</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5643</v>
+        <v>1.5167</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3482</v>
+        <v>0.7575</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2162</v>
+        <v>0.7591</v>
       </c>
       <c r="V17" t="n">
         <v>0.8837</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.623</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>0.035</v>
+        <v>0.1373</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5881</v>
+        <v>0.8582</v>
       </c>
       <c r="G18" t="n">
         <v>1.458</v>
@@ -1858,13 +1858,13 @@
         <v>0.5875</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2256</v>
+        <v>0.1469</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1012</v>
+        <v>0.0012</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1244</v>
+        <v>0.1457</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2178</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6315</v>
+        <v>-2.6048</v>
       </c>
       <c r="E19" t="n">
         <v>-0.0765</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5549</v>
+        <v>-2.5282</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9046</v>
@@ -1936,13 +1936,13 @@
         <v>0.1958</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7062</v>
+        <v>-0.6794</v>
       </c>
       <c r="T19" t="n">
         <v>-0.1782</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.528</v>
+        <v>-0.5012</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2166</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.9056</v>
+        <v>-4.0853</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7731</v>
+        <v>-0.8754</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.1325</v>
+        <v>-3.2099</v>
       </c>
       <c r="G20" t="n">
         <v>1.4515</v>
@@ -2014,13 +2014,13 @@
         <v>0.7834</v>
       </c>
       <c r="S20" t="n">
-        <v>1.7212</v>
+        <v>1.5415</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1863</v>
+        <v>1.0839</v>
       </c>
       <c r="U20" t="n">
-        <v>0.535</v>
+        <v>0.4576</v>
       </c>
       <c r="V20" t="n">
         <v>-4.924</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>25.3219</v>
+        <v>27.3686</v>
       </c>
       <c r="E21" t="n">
-        <v>13.6679</v>
+        <v>13.668</v>
       </c>
       <c r="F21" t="n">
-        <v>11.654</v>
+        <v>13.7008</v>
       </c>
       <c r="G21" t="n">
         <v>19.3009</v>
@@ -2092,13 +2092,13 @@
         <v>13.7093</v>
       </c>
       <c r="S21" t="n">
-        <v>6.5899</v>
+        <v>8.636800000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>4.469799999999999</v>
+        <v>4.4698</v>
       </c>
       <c r="U21" t="n">
-        <v>2.120400000000001</v>
+        <v>4.167</v>
       </c>
       <c r="V21" t="n">
         <v>1.3894</v>
